--- a/Versão5/PRO/Ontologia_Materiais.xlsx
+++ b/Versão5/PRO/Ontologia_Materiais.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6331B732-5466-4989-B11D-19721CDFDA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9E6B8E-0D40-4E68-BF22-9645F693D1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -4850,15 +4850,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <font>
         <b val="0"/>
@@ -5350,15 +5342,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="2" max="2" width="25.84375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
@@ -5369,7 +5361,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
@@ -5380,7 +5372,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
@@ -5391,7 +5383,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -5402,7 +5394,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -5414,7 +5406,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -5426,7 +5418,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -5437,7 +5429,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
@@ -5448,7 +5440,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -5459,7 +5451,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
@@ -5470,7 +5462,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -5481,7 +5473,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
@@ -5492,7 +5484,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
@@ -5503,7 +5495,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
@@ -5514,7 +5506,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -5525,7 +5517,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
@@ -5536,7 +5528,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
@@ -5547,19 +5539,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="39">
         <f ca="1">NOW()</f>
-        <v>46259.690755208336</v>
+        <v>46264.568710185187</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>79</v>
       </c>
@@ -5570,7 +5562,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
         <v>93</v>
       </c>
@@ -5581,7 +5573,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
         <v>90</v>
       </c>
@@ -5593,7 +5585,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>94</v>
       </c>
@@ -5605,7 +5597,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>56</v>
       </c>
@@ -5616,7 +5608,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="8" t="s">
         <v>57</v>
       </c>
@@ -5627,7 +5619,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>58</v>
       </c>
@@ -5638,7 +5630,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>59</v>
       </c>
@@ -5650,7 +5642,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
         <v>84</v>
       </c>
@@ -5672,36 +5664,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{784EFDB4-A2AF-4159-99A7-D6958B699B1B}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC289"/>
-  <sheetFormatPr defaultColWidth="16.7109375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16.69140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="51" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" style="51" customWidth="1"/>
+    <col min="2" max="2" width="4.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.84375" style="60" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="103" style="60" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="110.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="96.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="8.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.42578125" style="60" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="110.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="96.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="8.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.3828125" style="60" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.84375" style="60" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="60" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="16.7109375" style="60"/>
+    <col min="29" max="29" width="9.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="16.69140625" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -5790,7 +5782,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="54">
         <v>2</v>
       </c>
@@ -5887,7 +5879,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="54">
         <v>3</v>
       </c>
@@ -5984,7 +5976,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="54">
         <v>4</v>
       </c>
@@ -6081,7 +6073,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="54">
         <v>5</v>
       </c>
@@ -6178,7 +6170,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="54">
         <v>6</v>
       </c>
@@ -6275,7 +6267,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="54">
         <v>7</v>
       </c>
@@ -6372,7 +6364,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="54">
         <v>8</v>
       </c>
@@ -6469,7 +6461,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="54">
         <v>9</v>
       </c>
@@ -6566,7 +6558,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="54">
         <v>10</v>
       </c>
@@ -6663,7 +6655,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="54">
         <v>11</v>
       </c>
@@ -6760,7 +6752,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="54">
         <v>12</v>
       </c>
@@ -6857,7 +6849,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="54">
         <v>13</v>
       </c>
@@ -6954,7 +6946,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="54">
         <v>14</v>
       </c>
@@ -7051,7 +7043,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="54">
         <v>15</v>
       </c>
@@ -7148,7 +7140,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="54">
         <v>16</v>
       </c>
@@ -7245,7 +7237,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="54">
         <v>17</v>
       </c>
@@ -7342,7 +7334,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="54">
         <v>18</v>
       </c>
@@ -7439,7 +7431,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="54">
         <v>19</v>
       </c>
@@ -7536,7 +7528,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="54">
         <v>20</v>
       </c>
@@ -7633,7 +7625,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="54">
         <v>21</v>
       </c>
@@ -7730,7 +7722,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="54">
         <v>22</v>
       </c>
@@ -7827,7 +7819,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="54">
         <v>23</v>
       </c>
@@ -7924,7 +7916,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="54">
         <v>24</v>
       </c>
@@ -8021,7 +8013,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="54">
         <v>25</v>
       </c>
@@ -8118,7 +8110,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="54">
         <v>26</v>
       </c>
@@ -8215,7 +8207,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="54">
         <v>27</v>
       </c>
@@ -8312,7 +8304,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="54">
         <v>28</v>
       </c>
@@ -8409,7 +8401,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="54">
         <v>29</v>
       </c>
@@ -8506,7 +8498,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="54">
         <v>30</v>
       </c>
@@ -8603,7 +8595,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="54">
         <v>31</v>
       </c>
@@ -8700,7 +8692,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="54">
         <v>32</v>
       </c>
@@ -8797,7 +8789,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="54">
         <v>33</v>
       </c>
@@ -8894,7 +8886,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="54">
         <v>34</v>
       </c>
@@ -8991,7 +8983,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="54">
         <v>35</v>
       </c>
@@ -9088,7 +9080,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="54">
         <v>36</v>
       </c>
@@ -9185,7 +9177,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="54">
         <v>37</v>
       </c>
@@ -9282,7 +9274,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="54">
         <v>38</v>
       </c>
@@ -9379,7 +9371,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="54">
         <v>39</v>
       </c>
@@ -9476,7 +9468,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="54">
         <v>40</v>
       </c>
@@ -9573,7 +9565,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="54">
         <v>41</v>
       </c>
@@ -9670,7 +9662,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="54">
         <v>42</v>
       </c>
@@ -9767,7 +9759,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="54">
         <v>43</v>
       </c>
@@ -9864,7 +9856,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="54">
         <v>44</v>
       </c>
@@ -9961,7 +9953,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="54">
         <v>45</v>
       </c>
@@ -10058,7 +10050,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="54">
         <v>46</v>
       </c>
@@ -10155,7 +10147,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="54">
         <v>47</v>
       </c>
@@ -10252,7 +10244,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="54">
         <v>48</v>
       </c>
@@ -10349,7 +10341,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="54">
         <v>49</v>
       </c>
@@ -10446,7 +10438,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="54">
         <v>50</v>
       </c>
@@ -10543,7 +10535,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="54">
         <v>51</v>
       </c>
@@ -10640,7 +10632,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="54">
         <v>52</v>
       </c>
@@ -10737,7 +10729,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="54">
         <v>53</v>
       </c>
@@ -10834,7 +10826,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="54">
         <v>54</v>
       </c>
@@ -10931,7 +10923,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="54">
         <v>55</v>
       </c>
@@ -11028,7 +11020,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="54">
         <v>56</v>
       </c>
@@ -11125,7 +11117,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="54">
         <v>57</v>
       </c>
@@ -11222,7 +11214,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="54">
         <v>58</v>
       </c>
@@ -11319,7 +11311,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="54">
         <v>59</v>
       </c>
@@ -11416,7 +11408,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="54">
         <v>60</v>
       </c>
@@ -11513,7 +11505,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="54">
         <v>61</v>
       </c>
@@ -11610,7 +11602,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="54">
         <v>62</v>
       </c>
@@ -11707,7 +11699,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="54">
         <v>63</v>
       </c>
@@ -11804,7 +11796,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="54">
         <v>64</v>
       </c>
@@ -11901,7 +11893,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="54">
         <v>65</v>
       </c>
@@ -11998,7 +11990,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="54">
         <v>66</v>
       </c>
@@ -12095,7 +12087,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="54">
         <v>67</v>
       </c>
@@ -12192,7 +12184,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="54">
         <v>68</v>
       </c>
@@ -12289,7 +12281,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="54">
         <v>69</v>
       </c>
@@ -12386,7 +12378,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="70" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="54">
         <v>70</v>
       </c>
@@ -12483,7 +12475,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="71" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="54">
         <v>71</v>
       </c>
@@ -12580,7 +12572,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="72" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="54">
         <v>72</v>
       </c>
@@ -12677,7 +12669,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="73" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="54">
         <v>73</v>
       </c>
@@ -12774,7 +12766,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="74" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="54">
         <v>74</v>
       </c>
@@ -12871,7 +12863,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="75" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="54">
         <v>75</v>
       </c>
@@ -12968,7 +12960,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="76" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="54">
         <v>76</v>
       </c>
@@ -13065,7 +13057,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="77" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="54">
         <v>77</v>
       </c>
@@ -13162,7 +13154,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="78" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="54">
         <v>78</v>
       </c>
@@ -13259,7 +13251,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="79" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="54">
         <v>79</v>
       </c>
@@ -13356,7 +13348,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="54">
         <v>80</v>
       </c>
@@ -13453,7 +13445,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="54">
         <v>81</v>
       </c>
@@ -13550,7 +13542,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="54">
         <v>82</v>
       </c>
@@ -13647,7 +13639,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="54">
         <v>83</v>
       </c>
@@ -13744,7 +13736,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="54">
         <v>84</v>
       </c>
@@ -13841,7 +13833,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="54">
         <v>85</v>
       </c>
@@ -13938,7 +13930,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="54">
         <v>86</v>
       </c>
@@ -14035,7 +14027,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="54">
         <v>87</v>
       </c>
@@ -14132,7 +14124,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="54">
         <v>88</v>
       </c>
@@ -14229,7 +14221,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="54">
         <v>89</v>
       </c>
@@ -14326,7 +14318,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="54">
         <v>90</v>
       </c>
@@ -14423,7 +14415,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="54">
         <v>91</v>
       </c>
@@ -14520,7 +14512,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="54">
         <v>92</v>
       </c>
@@ -14617,7 +14609,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="54">
         <v>93</v>
       </c>
@@ -14714,7 +14706,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="54">
         <v>94</v>
       </c>
@@ -14811,7 +14803,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="54">
         <v>95</v>
       </c>
@@ -14908,7 +14900,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="54">
         <v>96</v>
       </c>
@@ -15005,7 +14997,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="54">
         <v>97</v>
       </c>
@@ -15102,7 +15094,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="54">
         <v>98</v>
       </c>
@@ -15199,7 +15191,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="54">
         <v>99</v>
       </c>
@@ -15296,7 +15288,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="54">
         <v>100</v>
       </c>
@@ -15393,7 +15385,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="54">
         <v>101</v>
       </c>
@@ -15490,7 +15482,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="54">
         <v>102</v>
       </c>
@@ -15587,7 +15579,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="54">
         <v>103</v>
       </c>
@@ -15684,7 +15676,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="54">
         <v>104</v>
       </c>
@@ -15781,7 +15773,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="54">
         <v>105</v>
       </c>
@@ -15878,7 +15870,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="54">
         <v>106</v>
       </c>
@@ -15975,7 +15967,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="54">
         <v>107</v>
       </c>
@@ -16072,7 +16064,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="54">
         <v>108</v>
       </c>
@@ -16169,7 +16161,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="54">
         <v>109</v>
       </c>
@@ -16266,7 +16258,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="54">
         <v>110</v>
       </c>
@@ -16363,7 +16355,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="54">
         <v>111</v>
       </c>
@@ -16460,7 +16452,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="54">
         <v>112</v>
       </c>
@@ -16557,7 +16549,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="54">
         <v>113</v>
       </c>
@@ -16654,7 +16646,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="54">
         <v>114</v>
       </c>
@@ -16751,7 +16743,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="54">
         <v>115</v>
       </c>
@@ -16848,7 +16840,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="54">
         <v>116</v>
       </c>
@@ -16945,7 +16937,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="54">
         <v>117</v>
       </c>
@@ -17042,7 +17034,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="54">
         <v>118</v>
       </c>
@@ -17139,7 +17131,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="54">
         <v>119</v>
       </c>
@@ -17236,7 +17228,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="54">
         <v>120</v>
       </c>
@@ -17333,7 +17325,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="54">
         <v>121</v>
       </c>
@@ -17430,7 +17422,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="54">
         <v>122</v>
       </c>
@@ -17527,7 +17519,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="54">
         <v>123</v>
       </c>
@@ -17624,7 +17616,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="54">
         <v>124</v>
       </c>
@@ -17721,7 +17713,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="54">
         <v>125</v>
       </c>
@@ -17818,7 +17810,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="54">
         <v>126</v>
       </c>
@@ -17915,7 +17907,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="54">
         <v>127</v>
       </c>
@@ -18012,7 +18004,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="54">
         <v>128</v>
       </c>
@@ -18109,7 +18101,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="54">
         <v>129</v>
       </c>
@@ -18206,7 +18198,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="54">
         <v>130</v>
       </c>
@@ -18303,7 +18295,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="54">
         <v>131</v>
       </c>
@@ -18400,7 +18392,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="54">
         <v>132</v>
       </c>
@@ -18497,7 +18489,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="54">
         <v>133</v>
       </c>
@@ -18594,7 +18586,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="54">
         <v>134</v>
       </c>
@@ -18691,7 +18683,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="54">
         <v>135</v>
       </c>
@@ -18788,7 +18780,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="54">
         <v>136</v>
       </c>
@@ -18885,7 +18877,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="54">
         <v>137</v>
       </c>
@@ -18982,7 +18974,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="54">
         <v>138</v>
       </c>
@@ -19079,7 +19071,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="139" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="54">
         <v>139</v>
       </c>
@@ -19176,7 +19168,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="140" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="54">
         <v>140</v>
       </c>
@@ -19273,7 +19265,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="141" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="54">
         <v>141</v>
       </c>
@@ -19370,7 +19362,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="142" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="54">
         <v>142</v>
       </c>
@@ -19467,7 +19459,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="143" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="54">
         <v>143</v>
       </c>
@@ -19564,7 +19556,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="144" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="54">
         <v>144</v>
       </c>
@@ -19661,7 +19653,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="145" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="54">
         <v>145</v>
       </c>
@@ -19758,7 +19750,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="146" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="54">
         <v>146</v>
       </c>
@@ -19855,7 +19847,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="147" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="54">
         <v>147</v>
       </c>
@@ -19952,7 +19944,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="148" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="54">
         <v>148</v>
       </c>
@@ -20049,7 +20041,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="149" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="54">
         <v>149</v>
       </c>
@@ -20146,7 +20138,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="150" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="54">
         <v>150</v>
       </c>
@@ -20243,7 +20235,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="151" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="54">
         <v>151</v>
       </c>
@@ -20340,7 +20332,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="152" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="54">
         <v>152</v>
       </c>
@@ -20437,7 +20429,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="153" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="54">
         <v>153</v>
       </c>
@@ -20534,7 +20526,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="154" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="54">
         <v>154</v>
       </c>
@@ -20631,7 +20623,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="155" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="54">
         <v>155</v>
       </c>
@@ -20728,7 +20720,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="156" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="54">
         <v>156</v>
       </c>
@@ -20825,7 +20817,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="157" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="54">
         <v>157</v>
       </c>
@@ -20922,7 +20914,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="158" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="54">
         <v>158</v>
       </c>
@@ -21019,7 +21011,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="159" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="54">
         <v>159</v>
       </c>
@@ -21116,7 +21108,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="160" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="54">
         <v>160</v>
       </c>
@@ -21213,7 +21205,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="161" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="54">
         <v>161</v>
       </c>
@@ -21310,7 +21302,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="162" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="54">
         <v>162</v>
       </c>
@@ -21407,7 +21399,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="163" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="54">
         <v>163</v>
       </c>
@@ -21504,7 +21496,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="164" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="54">
         <v>164</v>
       </c>
@@ -21601,7 +21593,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="165" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29" s="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="54">
         <v>165</v>
       </c>
@@ -21698,7 +21690,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="166" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="54">
         <v>166</v>
       </c>
@@ -21795,7 +21787,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="167" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="54">
         <v>167</v>
       </c>
@@ -21892,7 +21884,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="168" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="54">
         <v>168</v>
       </c>
@@ -21989,7 +21981,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="169" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="54">
         <v>169</v>
       </c>
@@ -22086,7 +22078,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="170" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="54">
         <v>170</v>
       </c>
@@ -22183,7 +22175,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="171" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="54">
         <v>171</v>
       </c>
@@ -22280,7 +22272,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="172" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="54">
         <v>172</v>
       </c>
@@ -22377,7 +22369,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="173" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="54">
         <v>173</v>
       </c>
@@ -22474,7 +22466,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="174" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="54">
         <v>174</v>
       </c>
@@ -22571,7 +22563,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="175" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="54">
         <v>175</v>
       </c>
@@ -22668,7 +22660,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="176" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="54">
         <v>176</v>
       </c>
@@ -22765,7 +22757,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="177" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="54">
         <v>177</v>
       </c>
@@ -22862,7 +22854,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="178" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="54">
         <v>178</v>
       </c>
@@ -22959,7 +22951,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="179" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="54">
         <v>179</v>
       </c>
@@ -23056,7 +23048,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="180" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="54">
         <v>180</v>
       </c>
@@ -23153,7 +23145,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="181" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="54">
         <v>181</v>
       </c>
@@ -23250,7 +23242,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="182" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="54">
         <v>182</v>
       </c>
@@ -23347,7 +23339,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="183" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="54">
         <v>183</v>
       </c>
@@ -23444,7 +23436,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="184" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="54">
         <v>184</v>
       </c>
@@ -23541,7 +23533,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="185" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="54">
         <v>185</v>
       </c>
@@ -23638,7 +23630,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="186" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="54">
         <v>186</v>
       </c>
@@ -23735,7 +23727,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="187" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="54">
         <v>187</v>
       </c>
@@ -23832,7 +23824,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="188" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="54">
         <v>188</v>
       </c>
@@ -23929,7 +23921,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="189" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="54">
         <v>189</v>
       </c>
@@ -24026,7 +24018,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="190" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="54">
         <v>190</v>
       </c>
@@ -24123,7 +24115,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="191" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="54">
         <v>191</v>
       </c>
@@ -24220,7 +24212,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="192" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="54">
         <v>192</v>
       </c>
@@ -24317,7 +24309,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="193" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="54">
         <v>193</v>
       </c>
@@ -24414,7 +24406,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="194" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="54">
         <v>194</v>
       </c>
@@ -24511,7 +24503,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="195" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="54">
         <v>195</v>
       </c>
@@ -24608,7 +24600,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="196" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="54">
         <v>196</v>
       </c>
@@ -24705,7 +24697,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="197" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="54">
         <v>197</v>
       </c>
@@ -24802,7 +24794,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="198" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="54">
         <v>198</v>
       </c>
@@ -24899,7 +24891,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="199" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="54">
         <v>199</v>
       </c>
@@ -24996,7 +24988,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="200" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="54">
         <v>200</v>
       </c>
@@ -25093,7 +25085,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="201" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="54">
         <v>201</v>
       </c>
@@ -25190,7 +25182,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="202" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="54">
         <v>202</v>
       </c>
@@ -25287,7 +25279,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="203" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="54">
         <v>203</v>
       </c>
@@ -25384,7 +25376,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="204" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="54">
         <v>204</v>
       </c>
@@ -25481,7 +25473,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="205" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="54">
         <v>205</v>
       </c>
@@ -25578,7 +25570,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="206" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="54">
         <v>206</v>
       </c>
@@ -25675,7 +25667,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="207" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="54">
         <v>207</v>
       </c>
@@ -25772,7 +25764,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="208" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="54">
         <v>208</v>
       </c>
@@ -25869,7 +25861,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="209" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="54">
         <v>209</v>
       </c>
@@ -25966,7 +25958,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="210" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="54">
         <v>210</v>
       </c>
@@ -26063,7 +26055,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="211" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="54">
         <v>211</v>
       </c>
@@ -26160,7 +26152,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="212" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="54">
         <v>212</v>
       </c>
@@ -26257,7 +26249,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="213" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="54">
         <v>213</v>
       </c>
@@ -26354,7 +26346,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="214" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="54">
         <v>214</v>
       </c>
@@ -26451,7 +26443,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="215" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="54">
         <v>215</v>
       </c>
@@ -26548,7 +26540,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="216" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="54">
         <v>216</v>
       </c>
@@ -26645,7 +26637,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="217" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="54">
         <v>217</v>
       </c>
@@ -26742,7 +26734,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="218" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="54">
         <v>218</v>
       </c>
@@ -26839,7 +26831,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="219" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="54">
         <v>219</v>
       </c>
@@ -26936,7 +26928,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="220" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="54">
         <v>220</v>
       </c>
@@ -27033,7 +27025,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="221" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="54">
         <v>221</v>
       </c>
@@ -27130,7 +27122,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="222" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="54">
         <v>222</v>
       </c>
@@ -27227,7 +27219,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="223" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="54">
         <v>223</v>
       </c>
@@ -27324,7 +27316,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="224" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="54">
         <v>224</v>
       </c>
@@ -27421,7 +27413,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="225" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="54">
         <v>225</v>
       </c>
@@ -27518,7 +27510,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="226" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="54">
         <v>226</v>
       </c>
@@ -27615,7 +27607,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="227" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="54">
         <v>227</v>
       </c>
@@ -27712,7 +27704,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="228" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="54">
         <v>228</v>
       </c>
@@ -27809,7 +27801,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="229" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="54">
         <v>229</v>
       </c>
@@ -27906,7 +27898,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="230" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="54">
         <v>230</v>
       </c>
@@ -28003,7 +27995,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="231" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="54">
         <v>231</v>
       </c>
@@ -28100,7 +28092,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="232" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="54">
         <v>232</v>
       </c>
@@ -28197,7 +28189,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="233" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="54">
         <v>233</v>
       </c>
@@ -28294,7 +28286,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="234" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="54">
         <v>234</v>
       </c>
@@ -28391,7 +28383,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="235" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="54">
         <v>235</v>
       </c>
@@ -28488,7 +28480,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="236" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="54">
         <v>236</v>
       </c>
@@ -28585,7 +28577,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="237" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="54">
         <v>237</v>
       </c>
@@ -28682,7 +28674,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="238" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="54">
         <v>238</v>
       </c>
@@ -28779,7 +28771,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="239" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="54">
         <v>239</v>
       </c>
@@ -28876,7 +28868,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="240" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="54">
         <v>240</v>
       </c>
@@ -28973,7 +28965,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="241" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="54">
         <v>241</v>
       </c>
@@ -29070,7 +29062,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="242" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="54">
         <v>242</v>
       </c>
@@ -29167,7 +29159,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="243" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="54">
         <v>243</v>
       </c>
@@ -29264,7 +29256,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="244" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="54">
         <v>244</v>
       </c>
@@ -29361,7 +29353,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="245" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="54">
         <v>245</v>
       </c>
@@ -29458,7 +29450,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="246" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="54">
         <v>246</v>
       </c>
@@ -29555,7 +29547,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="247" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="54">
         <v>247</v>
       </c>
@@ -29652,7 +29644,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="248" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="54">
         <v>248</v>
       </c>
@@ -29749,7 +29741,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="249" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="54">
         <v>249</v>
       </c>
@@ -29847,7 +29839,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="250" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="54">
         <v>250</v>
       </c>
@@ -29945,7 +29937,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="251" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="54">
         <v>251</v>
       </c>
@@ -30043,7 +30035,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="252" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="54">
         <v>252</v>
       </c>
@@ -30141,7 +30133,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="253" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="54">
         <v>253</v>
       </c>
@@ -30239,7 +30231,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="254" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="54">
         <v>254</v>
       </c>
@@ -30337,7 +30329,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="255" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="54">
         <v>255</v>
       </c>
@@ -30435,7 +30427,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="256" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="54">
         <v>256</v>
       </c>
@@ -30533,7 +30525,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="257" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="54">
         <v>257</v>
       </c>
@@ -30631,7 +30623,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="258" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="54">
         <v>258</v>
       </c>
@@ -30729,7 +30721,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="259" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="54">
         <v>259</v>
       </c>
@@ -30827,7 +30819,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="260" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="54">
         <v>260</v>
       </c>
@@ -30925,7 +30917,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="261" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="54">
         <v>261</v>
       </c>
@@ -31023,7 +31015,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="262" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="54">
         <v>262</v>
       </c>
@@ -31121,7 +31113,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="263" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="54">
         <v>263</v>
       </c>
@@ -31219,7 +31211,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="264" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="54">
         <v>264</v>
       </c>
@@ -31317,7 +31309,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="265" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="54">
         <v>265</v>
       </c>
@@ -31415,7 +31407,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="266" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="54">
         <v>266</v>
       </c>
@@ -31513,7 +31505,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="267" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="54">
         <v>267</v>
       </c>
@@ -31611,7 +31603,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="268" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="54">
         <v>268</v>
       </c>
@@ -31709,7 +31701,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="269" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="54">
         <v>269</v>
       </c>
@@ -31807,7 +31799,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="270" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="54">
         <v>270</v>
       </c>
@@ -31905,7 +31897,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="271" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="54">
         <v>271</v>
       </c>
@@ -32003,7 +31995,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="272" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="54">
         <v>272</v>
       </c>
@@ -32101,7 +32093,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="273" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="54">
         <v>273</v>
       </c>
@@ -32199,7 +32191,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="274" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="54">
         <v>274</v>
       </c>
@@ -32297,7 +32289,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="275" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="54">
         <v>275</v>
       </c>
@@ -32394,7 +32386,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="276" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="54">
         <v>276</v>
       </c>
@@ -32491,7 +32483,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="277" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="54">
         <v>277</v>
       </c>
@@ -32588,7 +32580,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="278" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="54">
         <v>278</v>
       </c>
@@ -32685,7 +32677,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="279" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="54">
         <v>279</v>
       </c>
@@ -32782,7 +32774,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="280" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="54">
         <v>280</v>
       </c>
@@ -32879,7 +32871,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="281" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="54">
         <v>281</v>
       </c>
@@ -32976,7 +32968,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="282" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="54">
         <v>282</v>
       </c>
@@ -33073,7 +33065,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="283" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="54">
         <v>283</v>
       </c>
@@ -33170,7 +33162,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="284" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="54">
         <v>284</v>
       </c>
@@ -33267,7 +33259,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="285" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="54">
         <v>285</v>
       </c>
@@ -33364,7 +33356,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="286" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="54">
         <v>286</v>
       </c>
@@ -33461,7 +33453,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="287" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="54">
         <v>287</v>
       </c>
@@ -33558,7 +33550,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="288" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="54">
         <v>288</v>
       </c>
@@ -33655,7 +33647,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="289" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="54">
         <v>289</v>
       </c>
@@ -33666,10 +33658,10 @@
         <v>1378</v>
       </c>
       <c r="D289" s="64" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E289" s="64" t="s">
         <v>1379</v>
-      </c>
-      <c r="E289" s="64" t="s">
-        <v>1380</v>
       </c>
       <c r="F289" s="64" t="s">
         <v>1381</v>
@@ -33695,11 +33687,11 @@
       </c>
       <c r="M289" s="23" t="str">
         <f t="shared" si="49"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N289" s="23" t="str">
         <f t="shared" si="49"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O289" s="23" t="str">
         <f t="shared" si="49"/>
@@ -33723,11 +33715,11 @@
       </c>
       <c r="U289" s="24" t="str">
         <f t="shared" si="53"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V289" s="65" t="str">
         <f t="shared" si="53"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W289" s="24" t="s">
         <v>830</v>
@@ -33758,53 +33750,53 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B289">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:C1 G1:Q1 S1:X1 AA1:XFD1">
-    <cfRule type="cellIs" dxfId="20" priority="592" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="592" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F121 F125:F288 F290:F1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289">
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q288">
-    <cfRule type="cellIs" dxfId="17" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R289">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y288 AA2:AA288">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC70:AC79">
-    <cfRule type="cellIs" dxfId="14" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="53" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC102">
-    <cfRule type="cellIs" dxfId="13" priority="418" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="418" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC105:AC106 AC164">
-    <cfRule type="cellIs" dxfId="12" priority="602" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="602" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC136:AC138">
-    <cfRule type="cellIs" dxfId="11" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="43" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33816,15 +33808,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.3046875" style="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
@@ -33889,7 +33881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -33957,7 +33949,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33970,14 +33962,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3828125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.15234375" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18">
         <v>1</v>
       </c>
@@ -33991,7 +33983,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -34005,7 +33997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -34019,7 +34011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -34033,13 +34025,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -34047,7 +34039,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="9" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34059,39 +34051,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BE003-A289-428E-9141-72F001D0AED0}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AC13"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.53515625" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.69140625" customWidth="1"/>
+    <col min="5" max="5" width="8.84375" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="34.5703125" customWidth="1"/>
-    <col min="8" max="8" width="6.85546875" customWidth="1"/>
-    <col min="9" max="9" width="39.140625" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" customWidth="1"/>
+    <col min="7" max="7" width="34.53515625" customWidth="1"/>
+    <col min="8" max="8" width="6.84375" customWidth="1"/>
+    <col min="9" max="9" width="39.15234375" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" style="53" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.53515625" style="53" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="4" customWidth="1"/>
-    <col min="17" max="17" width="11.5703125" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.53515625" customWidth="1"/>
+    <col min="18" max="18" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.3046875" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.69140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.69140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.69140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.69140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="34" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -34180,7 +34172,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="29">
         <v>2</v>
       </c>
@@ -34269,7 +34261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="29">
         <v>3</v>
       </c>
@@ -34358,7 +34350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="29">
         <v>4</v>
       </c>
@@ -34447,7 +34439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="29">
         <v>5</v>
       </c>
@@ -34536,7 +34528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="29">
         <v>6</v>
       </c>
@@ -34625,7 +34617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="29">
         <v>7</v>
       </c>
@@ -34714,7 +34706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="29">
         <v>8</v>
       </c>
@@ -34803,7 +34795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <v>9</v>
       </c>
@@ -34893,7 +34885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29">
         <v>10</v>
       </c>
@@ -34983,7 +34975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29">
         <v>11</v>
       </c>
@@ -35073,7 +35065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="29">
         <v>12</v>
       </c>
@@ -35163,7 +35155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" s="71" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29">
         <v>13</v>
       </c>
@@ -35255,36 +35247,31 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:D2 B3:B8 D3:D8 A3:A13 F1:S8">
-    <cfRule type="cellIs" dxfId="8" priority="44" operator="equal">
+  <conditionalFormatting sqref="A1:D2 F1:S8 B3:B8 D3:D8 A3:A13">
+    <cfRule type="cellIs" dxfId="7" priority="44" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B8">
-    <cfRule type="duplicateValues" dxfId="7" priority="1971"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1972"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1971"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1972"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:B13">
-    <cfRule type="duplicateValues" dxfId="5" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:E13">
-    <cfRule type="cellIs" dxfId="3" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H9:I13">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+  <conditionalFormatting sqref="H9:M13">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:AC13">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J9:M13">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
